--- a/measurements/27/Filled_2D_sections/axial/week27_axial_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/axial/week27_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,67 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +561,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.17995240928019</v>
+        <v>2736.848072562358</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70868072858671</v>
+        <v>306.6932904152643</v>
       </c>
       <c r="E2" t="n">
-        <v>11.74257899202952</v>
+        <v>229.2598755586715</v>
       </c>
       <c r="F2" t="n">
-        <v>1.337753890286729</v>
+        <v>1.33775389028673</v>
       </c>
       <c r="G2" t="n">
         <v>0.3656385716533773</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.391006097560976</v>
+        <v>1.735491071428571</v>
       </c>
       <c r="J2" t="n">
-        <v>1.391006097560976</v>
+        <v>27.15773809523809</v>
       </c>
       <c r="K2" t="n">
-        <v>1.391006097560976</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>9.680803571428571</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>27.15773809523809</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.477678571428571</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6.50297619047619</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5.530133928571428</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.735491071428571</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.304283164782868</v>
+      <c r="Z2" s="2" t="n">
+        <v>2784.240362811791</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +635,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.262046400951815</v>
+        <v>2768.140589569161</v>
       </c>
       <c r="D3" t="n">
-        <v>14.20629100392505</v>
+        <v>277.3609196004413</v>
       </c>
       <c r="E3" t="n">
-        <v>11.72829150572056</v>
+        <v>228.9809293974014</v>
       </c>
       <c r="F3" t="n">
         <v>1.211283928012518</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4521759611197929</v>
+        <v>0.452175961119793</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.128048780487805</v>
+        <v>1.372767857142857</v>
       </c>
       <c r="J3" t="n">
-        <v>1.128048780487805</v>
+        <v>22.02380952380952</v>
       </c>
       <c r="K3" t="n">
-        <v>1.128048780487805</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>8.622767857142858</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22.02380952380952</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.593005952380952</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.886160714285714</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.372767857142857</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.73389265479111</v>
+      <c r="Z3" s="2" t="n">
+        <v>248.6140946887788</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +709,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.232897085068412</v>
+        <v>2757.02947845805</v>
       </c>
       <c r="D4" t="n">
-        <v>14.06831893979049</v>
+        <v>274.6671793006715</v>
       </c>
       <c r="E4" t="n">
-        <v>11.69379850422464</v>
+        <v>228.3074946062905</v>
       </c>
       <c r="F4" t="n">
         <v>1.20305809397246</v>
@@ -619,24 +728,48 @@
         <v>0.4592379171970438</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.087747713414634</v>
+        <v>5.238095238095238</v>
       </c>
       <c r="J4" t="n">
-        <v>1.087747713414634</v>
+        <v>21.23697916666666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.087747713414634</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>10.35388764880952</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.23697916666666</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.097098214285714</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.843377976190475</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.21419332492642</v>
+      <c r="Z4" s="2" t="n">
+        <v>218.9437744390397</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +780,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.203747769185009</v>
+        <v>2745.918367346939</v>
       </c>
       <c r="D5" t="n">
-        <v>13.8125803964894</v>
+        <v>269.6741886933644</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67951105571375</v>
+        <v>228.0285491829827</v>
       </c>
       <c r="F5" t="n">
         <v>1.182633445064649</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4744808886415275</v>
+        <v>0.4744808886415277</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.039443597560976</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J5" t="n">
-        <v>1.039443597560976</v>
+        <v>20.29389880952381</v>
       </c>
       <c r="K5" t="n">
-        <v>1.039443597560976</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>9.993489583333332</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20.29389880952381</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.06547619047619</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.852678571428571</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Z5" s="2" t="n">
         <v>1.134535340550862</v>
       </c>
     </row>
@@ -694,17 +851,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.175788221296847</v>
+        <v>2735.260770975056</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67460834107748</v>
+        <v>266.9804485638936</v>
       </c>
       <c r="E6" t="n">
-        <v>11.71400403104177</v>
+        <v>228.7019834631965</v>
       </c>
       <c r="F6" t="n">
         <v>1.16737268527825</v>
@@ -713,23 +870,47 @@
         <v>0.4822249581893528</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.028868140243902</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J6" t="n">
-        <v>1.028868140243902</v>
+        <v>20.08742559523809</v>
       </c>
       <c r="K6" t="n">
-        <v>1.028868140243902</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>9.909784226190476</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20.08742559523809</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.96875</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.297247023809524</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.5777431996980464</v>
       </c>
     </row>
@@ -741,17 +922,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.16537775133849</v>
+        <v>2731.292517006802</v>
       </c>
       <c r="D7" t="n">
-        <v>13.03454394456817</v>
+        <v>254.4839532034738</v>
       </c>
       <c r="E7" t="n">
-        <v>11.74849707033576</v>
+        <v>229.3754189922696</v>
       </c>
       <c r="F7" t="n">
         <v>1.109464799329916</v>
@@ -760,24 +941,48 @@
         <v>0.5299773066710144</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7700076219512195</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7700076219512195</v>
+        <v>15.03348214285714</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7700076219512195</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.51469494047619</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15.03348214285714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.009672619047619</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.20610119047619</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.05</v>
+      <c r="Z7" s="2" t="n">
+        <v>4.05</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +993,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.149910767400358</v>
+        <v>2725.396825396825</v>
       </c>
       <c r="D8" t="n">
-        <v>12.84779140716646</v>
+        <v>250.8378322351547</v>
       </c>
       <c r="E8" t="n">
-        <v>11.59031948519916</v>
+        <v>226.2871899491265</v>
       </c>
       <c r="F8" t="n">
         <v>1.108493292490607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5443190474448526</v>
+        <v>0.5443190474448525</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7223704268292683</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7223704268292683</v>
+        <v>14.10342261904762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7223704268292683</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>8.452845982142856</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14.10342261904762</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.301711309523808</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.120535714285714</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7474911077235773</v>
+      <c r="Z8" s="2" t="n">
+        <v>2.546130952380952</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1064,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.237953599048186</v>
+        <v>2758.956916099773</v>
       </c>
       <c r="D9" t="n">
-        <v>12.55510843963158</v>
+        <v>245.1235457261403</v>
       </c>
       <c r="E9" t="n">
-        <v>11.59031947066144</v>
+        <v>226.2871896652948</v>
       </c>
       <c r="F9" t="n">
         <v>1.083240929761453</v>
@@ -854,24 +1083,48 @@
         <v>0.5770118368977174</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6341463414634146</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6341463414634146</v>
+        <v>12.38095238095238</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6341463414634146</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>7.88783482142857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.141741071428571</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.742931547619047</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7687478827913279</v>
+      <c r="Z9" s="2" t="n">
+        <v>14.45284598214286</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1135,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.323022010707913</v>
+        <v>2791.383219954648</v>
       </c>
       <c r="D10" t="n">
-        <v>12.76206655909376</v>
+        <v>249.1641566299257</v>
       </c>
       <c r="E10" t="n">
-        <v>11.40601829493918</v>
+        <v>222.6889286154792</v>
       </c>
       <c r="F10" t="n">
         <v>1.118888838250965</v>
       </c>
       <c r="G10" t="n">
-        <v>0.565012678112181</v>
+        <v>0.5650126781121811</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5992759146341463</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5992759146341463</v>
+        <v>11.70014880952381</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5992759146341463</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>7.506045386904761</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.70014880952381</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.953869047619047</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.084449404761904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7581194952574526</v>
+      <c r="Z10" s="2" t="n">
+        <v>7.276126922123015</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1206,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.444973230220107</v>
+        <v>2837.868480725623</v>
       </c>
       <c r="D11" t="n">
-        <v>12.22201446789067</v>
+        <v>238.6202824683416</v>
       </c>
       <c r="E11" t="n">
-        <v>11.26212814959084</v>
+        <v>219.879644825345</v>
       </c>
       <c r="F11" t="n">
         <v>1.085231343983126</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6263072190367026</v>
+        <v>0.6263072190367027</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5516387195121951</v>
+        <v>1.984747023809524</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5516387195121951</v>
+        <v>10.77008928571428</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5516387195121951</v>
+        <v>6.164899553571429</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.77008928571428</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.984747023809524</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1277,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.5116002379536</v>
+        <v>2863.265306122449</v>
       </c>
       <c r="D12" t="n">
-        <v>11.85687879818242</v>
+        <v>231.4914432026091</v>
       </c>
       <c r="E12" t="n">
-        <v>11.0290464860637</v>
+        <v>215.3290028231484</v>
       </c>
       <c r="F12" t="n">
         <v>1.075059282156872</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6714312802573249</v>
+        <v>0.6714312802573247</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.528296493902439</v>
+        <v>1.50483630952381</v>
       </c>
       <c r="J12" t="n">
-        <v>0.528296493902439</v>
+        <v>10.31436011904762</v>
       </c>
       <c r="K12" t="n">
-        <v>0.528296493902439</v>
+        <v>5.404575892857142</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.31436011904762</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.187872023809524</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.50483630952381</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>14.72019893483709</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1348,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.523200475907198</v>
+        <v>2867.687074829932</v>
       </c>
       <c r="D13" t="n">
-        <v>11.76176917552948</v>
+        <v>229.6345410460517</v>
       </c>
       <c r="E13" t="n">
-        <v>10.98026599535128</v>
+        <v>214.3766218140012</v>
       </c>
       <c r="F13" t="n">
         <v>1.071173428813935</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6833877579481411</v>
+        <v>0.683387757948141</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5051448170731707</v>
+        <v>1.104910714285714</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5051448170731707</v>
+        <v>9.86235119047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5051448170731707</v>
+        <v>4.951636904761904</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.86235119047619</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.052083333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.787202380952381</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.104910714285714</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>10.47619047619048</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1419,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.535693039857228</v>
+        <v>2872.448979591837</v>
       </c>
       <c r="D14" t="n">
-        <v>11.75339973554379</v>
+        <v>229.4711376939501</v>
       </c>
       <c r="E14" t="n">
-        <v>10.97189657281085</v>
+        <v>214.2132188024975</v>
       </c>
       <c r="F14" t="n">
         <v>1.071227718703579</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6854977755703439</v>
+        <v>0.685497775570344</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5264862804878049</v>
+        <v>0.9728422619047619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5264862804878049</v>
+        <v>10.27901785714286</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5264862804878049</v>
+        <v>4.885137648809524</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.27901785714286</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.033482142857142</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.255208333333333</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.9728422619047619</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="15">
@@ -1085,26 +1490,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.490481856038073</v>
+        <v>2855.215419501134</v>
       </c>
       <c r="D15" t="n">
-        <v>11.5094973168722</v>
+        <v>224.7092333294096</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8482119978928</v>
+        <v>211.7984247207642</v>
       </c>
       <c r="F15" t="n">
         <v>1.060958001107266</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7105700664009564</v>
+        <v>0.7105700664009563</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.845982142857143</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.37313988095238</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.589037698412699</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9.37313988095238</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.547991071428571</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.845982142857143</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>7.181570870535714</v>
       </c>
     </row>
     <row r="16">
@@ -1115,17 +1558,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.445270672218918</v>
+        <v>2837.981859410431</v>
       </c>
       <c r="D16" t="n">
-        <v>11.55827781049217</v>
+        <v>225.6616143953233</v>
       </c>
       <c r="E16" t="n">
-        <v>10.8398426044278</v>
+        <v>211.6350222769238</v>
       </c>
       <c r="F16" t="n">
         <v>1.066277272861038</v>
@@ -1134,7 +1577,48 @@
         <v>0.7003322043001273</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.09375</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.532180059523809</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.014880952380952</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.496279761904762</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.09375</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>5.892857142857143</v>
       </c>
     </row>
     <row r="17">
@@ -1145,17 +1629,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.385187388459251</v>
+        <v>2815.079365079365</v>
       </c>
       <c r="D17" t="n">
-        <v>12.10669931551305</v>
+        <v>236.368891398112</v>
       </c>
       <c r="E17" t="n">
-        <v>10.79106211080784</v>
+        <v>210.6826412110102</v>
       </c>
       <c r="F17" t="n">
         <v>1.121919157835959</v>
@@ -1164,16 +1648,48 @@
         <v>0.6331693311627494</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.501116071428571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10.32738095238095</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.980282738095238</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.5289634146341463</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.5205792682926829</v>
+      <c r="M17" t="n">
+        <v>10.32738095238095</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.092633928571428</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.501116071428571</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>4.635623346560847</v>
       </c>
     </row>
     <row r="18">
@@ -1184,35 +1700,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.327186198691256</v>
+        <v>2792.97052154195</v>
       </c>
       <c r="D18" t="n">
-        <v>12.0840424357391</v>
+        <v>235.9265427930014</v>
       </c>
       <c r="E18" t="n">
-        <v>10.74228163754068</v>
+        <v>209.7302605424608</v>
       </c>
       <c r="F18" t="n">
         <v>1.124904637903871</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6305544697243269</v>
+        <v>0.6305544697243268</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5521150914634146</v>
+        <v>1.681547619047619</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5521150914634146</v>
+        <v>10.77938988095238</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5521150914634146</v>
+        <v>6.039806547619048</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10.77938988095238</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.174479166666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.681547619047619</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="19">
@@ -1223,17 +1771,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.279298036882809</v>
+        <v>2774.716553287982</v>
       </c>
       <c r="D19" t="n">
-        <v>12.0377132979835</v>
+        <v>235.0220215320587</v>
       </c>
       <c r="E19" t="n">
-        <v>10.69350114101317</v>
+        <v>208.7778794197809</v>
       </c>
       <c r="F19" t="n">
         <v>1.125703653017329</v>
@@ -1242,16 +1790,48 @@
         <v>0.6312645104356045</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7317073170731707</v>
+        <v>1.709449404761905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7317073170731707</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7317073170731707</v>
+        <v>6.139787946428571</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.491815476190475</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.072172619047619</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.709449404761905</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1.972441620879121</v>
       </c>
     </row>
     <row r="20">
@@ -1262,35 +1842,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.195716835217133</v>
+        <v>2742.857142857143</v>
       </c>
       <c r="D20" t="n">
-        <v>12.60042223116247</v>
+        <v>246.008243560791</v>
       </c>
       <c r="E20" t="n">
-        <v>10.69941919315152</v>
+        <v>208.8934223424821</v>
       </c>
       <c r="F20" t="n">
         <v>1.177673479624739</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5695262320380933</v>
+        <v>0.5695262320380932</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.341145833333333</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.361886160714286</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5609756097560976</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.7560975609756098</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6585365853658537</v>
+      <c r="M20" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.392113095238095</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.341145833333333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>1.408110119047619</v>
       </c>
     </row>
     <row r="21">
@@ -1301,35 +1913,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.016359309934563</v>
+        <v>2674.489795918367</v>
       </c>
       <c r="D21" t="n">
-        <v>12.5171487505843</v>
+        <v>244.3824279875982</v>
       </c>
       <c r="E21" t="n">
-        <v>10.53287220001221</v>
+        <v>205.6417905716669</v>
       </c>
       <c r="F21" t="n">
         <v>1.188388932561984</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5627439811596985</v>
+        <v>0.5627439811596986</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.551153273809524</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5853658536585367</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7560975609756098</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.6707317073170732</v>
+      <c r="M21" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.892485119047619</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1339,7 +1983,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1362,6 +2006,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/27/Filled_2D_sections/axial/week27_axial_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/axial/week27_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2043,4 +2249,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week27_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2784.240362811791</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.53871862142545</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2674.489795918367</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2872.448979591837</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>248.6140946887788</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.0880744235529</v>
+      </c>
+      <c r="E11" t="n">
+        <v>224.7092333294096</v>
+      </c>
+      <c r="F11" t="n">
+        <v>306.6932904152643</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.134535340550862</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0682921540922011</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.060958001107266</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.33775389028673</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5777431996980464</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.09562649267594292</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3656385716533773</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7105700664009563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3940344628262061</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4893604849295929</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.190974832912761</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8255779474818965</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>23</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.98211050724638</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.897083606354489</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="F48" t="n">
+        <v>27.15773809523809</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>39</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.131429334554335</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.586245335703967</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.255208333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.37313988095238</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>19</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.79423167293233</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5858828144719214</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9728422619047619</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.892485119047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>